--- a/daily_matches/job_matches_2026-06-18.xlsx
+++ b/daily_matches/job_matches_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Sr. Data Science &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>32.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, MLflow, Docker</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, XGBoost</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d876dbf0ef129abd</t>
+          <t>https://www.indeed.com/viewjob?jk=485e857894cb3c80</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Digital Site Reliability Sr Engineer - Remote</t>
+          <t>AI engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02dd332b5bab760b</t>
+          <t>https://www.indeed.com/viewjob?jk=eae97d5c495bfdbf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Elanco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, AKS, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Synapse, CI/CD, Git, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69480e4fa81c61</t>
+          <t>https://www.indeed.com/viewjob?jk=e373c911fb44afc4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Hybrid)</t>
+          <t>JAVA Software Development Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KnowBe4</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, CI/CD, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dadf60f6511d26fa</t>
+          <t>https://www.indeed.com/viewjob?jk=3fecd8003f1e49fe</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer 2, DevOps</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,487 +636,487 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63ccf9e53d6a2ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=89cb558bb9ed5195</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Expert Consultant, Coro, AI Engineer</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ec0a48702df4aa</t>
+          <t>https://www.indeed.com/viewjob?jk=75fa0e025deb7ffa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Expert Consultant, Coro, AI Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c7e3b2609a13d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=a571ee3df1f1827f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Expert Consultant, Coro, AI Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9449bb7c13a58d3</t>
+          <t>https://www.indeed.com/viewjob?jk=af8d3c26dac4d434</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Expert Consultant, Coro, AI Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=816e02110f95bb31</t>
+          <t>https://www.indeed.com/viewjob?jk=f87945604cbcf047</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Expert Consultant, Coro, AI Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19cb6c64bf2bd39</t>
+          <t>https://www.indeed.com/viewjob?jk=07f7c360e2c19b02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Expert Consultant, Coro, AI Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec69001c086a8450</t>
+          <t>https://www.indeed.com/viewjob?jk=9a8b16e23041fe8f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Expert Consultant, Coro, AI Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d1c67b26cc06b16</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0256d1a4825c51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Expert Consultant, Coro, AI Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0445e516cc6665</t>
+          <t>https://www.indeed.com/viewjob?jk=92af6eea4c158a18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Expert Consultant, Coro, AI Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedaab3df5744184</t>
+          <t>https://www.indeed.com/viewjob?jk=41a051758456fb2c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Expert Consultant, Coro, AI Engineer</t>
+          <t>Sr. Data Engineer - Data Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+          <t>RAG, S3, EC2, Glue, Athena, Redshift, Redshift, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8e8f640ae93f45</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e97837c318154e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Expert Consultant, Coro, AI Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+          <t>RAG, Glue, Athena, Redshift, Redshift, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289c0e37c50fc7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=8466e5e68d3f0410</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Expert Consultant, Coro, AI Engineer</t>
+          <t>Nuuly Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nuuly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01f6eb19214663a</t>
+          <t>https://www.indeed.com/viewjob?jk=3092f86eafee7472</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, EC2, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e450dded81ba50a7</t>
+          <t>https://www.indeed.com/viewjob?jk=dc17eac11a96f0cf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Remote)</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, EC2, CI/CD, PySpark, Polars, Python, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, MySQL, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d94eaa0b111276c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b518bbb970613d5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marketing Data Scientist</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Puget Sound Energy</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, MySQL, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,42 +1161,4137 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f3a77bf18237855</t>
+          <t>https://www.indeed.com/viewjob?jk=6c90ecb8df08d12e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AML Surveillance Tools Engineer/Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, PyTorch, Docker, CI/CD, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a25029da8bd6898</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Engineer Junior or Senior</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e0843a70108cac0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sr. Full Stack Developer - Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Docker, Kubernetes, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4127d80f97fe9f35</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Kafka, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6611e3700ea8307d</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Kafka, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6785f9b978fbb0fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Epic Lab Software Engineer (NCG - Master's/PhD)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Applied Materials</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3751a2611f48a26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist - Advertising Technology</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60dc1d93afbdb0b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CNH Industrial</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sioux Falls, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fc5720383f3bb4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CNH Industrial</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sioux Falls, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3aeadafa4ab34495</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Cloud Architect - Kubernetes</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8cdb95905cfaf2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Cloud Architect - Kubernetes</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d28f7b9d9de584f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Cloud Architect - Kubernetes</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7ce8e6f35f2b566</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Cloud Architect - Kubernetes</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13f15c12809fedcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Cloud Architect - Kubernetes</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca134da0a1a2aa1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Cloud Architect - Kubernetes</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf0e14d03764707d</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Cloud Architect - Kubernetes</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab58c3fdb55b4c0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Cloud Architect - Kubernetes</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f29e4ac0228676b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Cloud Architect - Kubernetes</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04a5e1440e7a06b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Cloud Architect - Kubernetes</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba9206f8c7686399</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Cloud Architect - Kubernetes</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c698b96ffd16244b</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Cloud Architect - Kubernetes</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68f5e5ba350a5ed6</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Infra and DevOps Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a208ecb708f50e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Infra and DevOps Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cad09a703170a75c</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Infra and DevOps Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f719b5d37ae1f449</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Infra and DevOps Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6846f97b9dad19f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Infra and DevOps Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=167bb841f41ebd59</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Infra and DevOps Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bead62aa71321d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Infra and DevOps Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bf274b23e0b36fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Infra and DevOps Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce1c51221064ca81</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78b2b738cb721c63</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa7404cece78de0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58ca439d88830b14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5071cac27ea01cf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dd3ba906f3ed6f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b7e649c218fa703</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, Databricks, Kafka, Hadoop, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e31ddac5433848</t>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83a2d75baf65f89a</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2a927bd32a1d359</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62fd3a6095b1b22e</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59a7c7d90d073887</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df07f2b091c23646</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c7d741330a97a68</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f554d7f023d5ee3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2327b0a28f26f618</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=642fba959070f6d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ee5743ff90617a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e8620751b74b5ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56bac0ee53cdc304</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cdb5fa11b845c32</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3df3fc3bb1bd53a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1b32777a1865513</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=613fc1fe2d361083</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481767fe09962921</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a0494f5573f7269</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab100b62a6e419a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=973ef8649311c9f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb82db675ed7ad6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26af1b12b7b9be0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56fa216de6f0115a</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3870632a31c8986</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76b75863ab761835</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=970f6fb866b71684</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12e3efbba700c7fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f0de7138687e30b</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7e8fd5ebc072f44</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d0e8b99e71c22ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbae4f11d16e033c</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d473cb49be7b850c</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=353b73dfd398d980</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00dd0c6958020d7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=030de01bf565c7e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7ca6ae9f387c225</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=584427ece8548d2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1c1a3da9f0421aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3654432a2c1fc98</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c42e2bbea57ab853</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3c0a24e62f460a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51560a3004b7eae0</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8868975cd9a41533</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ab530b519e74555</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce271483f7ca8100</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70be26e2ba5098c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13d9508941c19ab1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3195ec4fdedf5390</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0cd7a4a13b6c7a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07819e8c63f9354f</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6be000e8262f017b</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1896530462534c78</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Lansing, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44eb680daad848fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da47e16cee18baf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b85d1b8bd606fa1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4148d91ecef8a6f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16fcd22611e09ff2</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4235e61cbd3674df</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f286927992b9dc87</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54cef4d844126aef</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58d8c01f0bbd727b</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19756c5d65bf0719</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44afc83ac14f0032</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Lansing, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d97f64a01208a939</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd8875e06f1455a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de36ddf51aed64aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75fe28f75170fe2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e393eed123e4356</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03cc4f8e3c3862b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce52e5268f32013f</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db975ef0e63eb28b</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aebb629c703b443c</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8b49ba6b720edb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92ef27e5fb8f8493</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46fba7701840a107</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33e50299b1439dbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8271a7e93ae9c9f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b9a9ad8158d19e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8effa586d04a5e1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=783cd8e105691684</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc8e7ef438f79ce9</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14c3f58b71702ad7</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Embedded Software Engineer (C++)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>DIVERGENT</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Torrance, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>RAG, OpenCV, CI/CD, GitHub Actions, Git, Python, R, C++, Scala</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15b13166bc399ab5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-18.xlsx
+++ b/daily_matches/job_matches_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Data Science &amp; AI Engineer</t>
+          <t>Specialist Engineer- Data</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Ollion</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.2</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, XGBoost</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, GCP Vertex AI, BigQuery, Synapse, Data Lake, Dataflow, MLflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,119 +496,119 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23a781e3d977eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=a967b71634e71edd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>NorthStar Advisory</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, LLaMA, Copilot, Prompt Engineering, S3, Glue, Athena, Kinesis</t>
+          <t>Data Scientist, Redshift, BigQuery, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe33d6ae05c1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=3cb780a0adb5f2e5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Cloud Platform Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bristol, CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, BigQuery, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git</t>
+          <t>Data Scientist, S3, EC2, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7408f2457ea00a</t>
+          <t>https://www.indeed.com/viewjob?jk=2df35197e791e2f5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Cloud Platform Engineer</t>
+          <t>Senior Software Engineer, Autonomous Lab</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>Ginkgo BioWorks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, BigQuery, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git</t>
+          <t>LangChain, RAG, BigQuery, Kubernetes, CI/CD, Git, Snowflake, BigQuery, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e7c464991cdd72</t>
+          <t>https://www.indeed.com/viewjob?jk=7be02d1647d171ab</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>AI engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,42 +618,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, CI/CD, Databricks</t>
+          <t>AI Engineer, RAG, Gemini, Hugging Face, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac584f9300ae9831</t>
+          <t>https://www.indeed.com/viewjob?jk=d7dc7fcef6ff4e43</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Machine Learning Engineer (174332)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, Hadoop, MySQL, Cassandra, NoSQL, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1b88b44add0b99</t>
+          <t>https://www.indeed.com/viewjob?jk=eca1a5640b3249e8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,77 +696,77 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, Cassandra</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, Glue, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333b83afb224e2fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c88b22a5e9ebd94b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, BigQuery, FastAPI, CI/CD, Git, BigQuery, NoSQL, Python</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d92813b6e702e2</t>
+          <t>https://www.indeed.com/viewjob?jk=dd72966a9cf0f195</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>IO Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26f585fd82f96ad5</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a972802f7925c4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TubeScience-Labs</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>RAG, CI/CD, Jenkins, Git, PostgreSQL, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624ea83782c1527b</t>
+          <t>https://www.indeed.com/viewjob?jk=0c96ade68c1d70c6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, SQL</t>
+          <t>Data Scientist, XGBoost, BigQuery, CI/CD, BigQuery, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909a2112f1981955</t>
+          <t>https://www.indeed.com/viewjob?jk=a876255773859a48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Analytics Engineer</t>
+          <t>Senior Data Analytics Engineer - Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Git, Snowflake, Databricks, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,102 +881,102 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f06818ad11d5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=0942a9e0c1a166d9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Software Engineer 2, Autonomous Lab</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Ginkgo BioWorks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Kafka, SQL, R</t>
+          <t>LangChain, RAG, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e05dd5a314ee99</t>
+          <t>https://www.indeed.com/viewjob?jk=266753facb8252c9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Systems Engineer - Cloud Ops</t>
+          <t>Product Software Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Bristol, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Pinecone, Prompt Engineering, Kubernetes, CI/CD, Terraform, Git, SQL, R</t>
+          <t>Data Scientist, RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba9c6c0f5989499</t>
+          <t>https://www.indeed.com/viewjob?jk=bac3831ddf5c36a7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Finance</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mortenson Construction</t>
+          <t>Palmer Holland</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Westlake, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Dataflow, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, MLflow, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611b25405f74a49d</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cea13d9bb9795e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Data Analytics Engineer - Boulder, Colorado</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SumUp</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Berwyn, IL, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, Git, Snowflake, Tableau, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,602 +1021,42 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e7b19213b39b6e</t>
+          <t>https://www.indeed.com/viewjob?jk=24cfcd2d6c81c0e0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Accounting</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AppFolio</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Python, SQL, R, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa39f9b270a5394</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Accounting</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>AppFolio</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65c4e747f036d1f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Accounting</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>AppFolio</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=024b56921b6d4764</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Accounting</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>AppFolio</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c247a1e7cf73177</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Accounting</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>AppFolio</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=850fff7472021adb</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Accounting</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>AppFolio</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74335a929a7ef72e</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Accounting</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>AppFolio</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd6b687aa97c1fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Accounting</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>AppFolio</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Santa Barbara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Apache Airflow, PySpark, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da2be6d24fd55a7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Databricks, Kafka, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=000424a308d6d5f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Developer -AWS Python SQL Big Data</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Intone Networks</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, EC2, CI/CD, Jenkins, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48d4e37895373efa</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer, DevX</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>BRAIN</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Databricks, Python, R</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85df86f84f42f998</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Engineer Senior- AI Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>PNC Financial Services Group</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e8027e834cf691b</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Software Engineer Senior- AI Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>PNC Financial Services Group</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=683caadf7073cd4a</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Associate - Associate Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, FastAPI, CI/CD, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a8258e130a7401e</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>AutoZone</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bceacdce68298953</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Beezwax Datatools, Inc.</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Cupertino, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dab786d95c0f6699</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Love’s Travel Stops</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1355cb2c685916</t>
+          <t>https://www.indeed.com/viewjob?jk=1b57b468bb0f2052</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-18.xlsx
+++ b/daily_matches/job_matches_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Specialist Engineer- Data</t>
+          <t>Machine Learning Engineer| AI - US</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ollion</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, GCP Vertex AI, BigQuery, Synapse, Data Lake, Dataflow, MLflow</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, XGBoost</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a967b71634e71edd</t>
+          <t>https://www.indeed.com/viewjob?jk=46b7a8d8a75a3102</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Solutions Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NorthStar Advisory</t>
+          <t>BKV Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, BigQuery</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, S3, Glue, Athena, Redshift, BigQuery, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cb780a0adb5f2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>GCP /Python Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bristol, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, MySQL</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2df35197e791e2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=a7204d512f6fb7e2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Autonomous Lab</t>
+          <t>GCP Python Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ginkgo BioWorks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, BigQuery, Kubernetes, CI/CD, Git, Snowflake, BigQuery, Kafka, PostgreSQL</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be02d1647d171ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ec5924f2fb72de</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,29 +626,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Hugging Face, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7dc7fcef6ff4e43</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8a93ff78250e07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (174332)</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, S3, CI/CD, Git, Snowflake, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca1a5640b3249e8</t>
+          <t>https://www.indeed.com/viewjob?jk=9616981e1f2836ce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, Glue, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88b22a5e9ebd94b</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fa52053f2d31b3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd72966a9cf0f195</t>
+          <t>https://www.indeed.com/viewjob?jk=63df1cb30c816e0b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IO Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a972802f7925c4</t>
+          <t>https://www.indeed.com/viewjob?jk=5b70eebfd6d08b3e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, PostgreSQL, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c96ade68c1d70c6</t>
+          <t>https://www.indeed.com/viewjob?jk=900a9829c2794aeb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Machine Learning (ML) Engineer (AI Insurtech)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EvolutionIQ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, XGBoost, BigQuery, CI/CD, BigQuery, PySpark, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Keras, BigQuery, Kubernetes, Terraform, BigQuery, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a876255773859a48</t>
+          <t>https://www.indeed.com/viewjob?jk=39cd074e0f4d340f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer - Remote</t>
+          <t>Senior Machine Learning (ML) Engineer (AI Insurtech)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>EvolutionIQ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Snowflake, Databricks, MySQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Keras, BigQuery, Kubernetes, Terraform, BigQuery, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0942a9e0c1a166d9</t>
+          <t>https://www.indeed.com/viewjob?jk=a1e470bd9e179e4b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer 2, Autonomous Lab</t>
+          <t>Senior Backend Engineer- AI Agent</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ginkgo BioWorks</t>
+          <t>Shanghai Xiaoxi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Optimization</t>
+          <t>LangChain, Gemini, Prompt Engineering, FastAPI, Kubernetes, CI/CD, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=266753facb8252c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bdc304307c73e2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Product Software Engineer II</t>
+          <t>AI Practitioner- PRN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rogers Behavioral Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bristol, CT, US USA</t>
+          <t>Oconomowoc, WI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac3831ddf5c36a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0cff99a9854d3ba8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Machine Learning Engineer, User Signal &amp; Ads</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Palmer Holland</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westlake, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, MLflow, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kafka, Hadoop, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cea13d9bb9795e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b8ec5f6ed88064c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer - Boulder, Colorado</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SumUp</t>
+          <t>REGARD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Git, Snowflake, Tableau, SQL, R, Scala</t>
+          <t>RAG, S3, Athena, FastAPI, Kubernetes, PySpark, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,357 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cfcd2d6c81c0e0</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8e6412b9b83a76</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>REGARD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, S3, Athena, FastAPI, Kubernetes, PySpark, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccb3bea9b095d4ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FULLTHROTTLE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Prompt Engineering, S3, Docker, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fe703dc5462eb40</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Platform Engineer - Palantir</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Acrisure LLC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Snowflake, Databricks, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9947f29081d0c0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Platform Engineer - Palantir</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Acrisure LLC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Snowflake, Databricks, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74450422ec001fb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Junior Software QA Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Telit Wireless Solutions</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b91213d94efecee</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Full-Stack Developer – Websites (On Call - Remote)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ca49d6a6128d3ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Part-time Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TNTP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bbf73d5f0d07a6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Snowflake, Python, SQL, R, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b57b468bb0f2052</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f16d6e07a42496a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer - Intern - Payments &amp; Wallets</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gen Digital Inc.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55baa703a2556a5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Git, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e2449a5591f29a5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-18.xlsx
+++ b/daily_matches/job_matches_2026-06-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer| AI - US</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, XGBoost</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, OpenCV, AWS SageMaker, GCP Vertex AI, Kinesis, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b7a8d8a75a3102</t>
+          <t>https://www.indeed.com/viewjob?jk=53640afa375309cf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer</t>
+          <t>Senior Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BKV Corporation</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, S3, Glue, Athena, Redshift, BigQuery, CI/CD</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Data Lake, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d3ae64d2ffc86a</t>
+          <t>https://www.indeed.com/viewjob?jk=810aff76fcea7f08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GCP /Python Data Engineer</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BetMGM LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, Git, BigQuery</t>
+          <t>Data Scientist, RAG, Copilot, Pinecone, Cortex, S3, Glue, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7204d512f6fb7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=fce20003ac2a826f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP Python Data Engineer</t>
+          <t>Sr. Software Engineer, AI Native</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, Git, BigQuery</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ec5924f2fb72de</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6dbb89d7f07724</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Sumter Electric Cooperative, Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sumterville, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
+          <t>RAG, Copilot, Synapse, Data Lake, Dataflow, CI/CD, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8a93ff78250e07</t>
+          <t>https://www.indeed.com/viewjob?jk=05a5a8eaa7d566a4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Senior AI Engineer | US | Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Grafana Labs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, CI/CD, Git, Snowflake, Databricks, PySpark, Python</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, Pinecone, ChromaDB, Prompt Engineering, BigQuery, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9616981e1f2836ce</t>
+          <t>https://www.indeed.com/viewjob?jk=4ace9dc91e148c51</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>BetMGM LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
+          <t>Data Scientist, RAG, Copilot, Cortex, S3, Glue, Kinesis, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fa52053f2d31b3</t>
+          <t>https://www.indeed.com/viewjob?jk=f66557aa16a0d567</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Asset Management Engineering - Associate Software Engineer (AI Engineering) - Dallas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63df1cb30c816e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=252af71079fd2a98</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>The Nielsen Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
+          <t>Data Scientist, RAG, Copilot, S3, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b70eebfd6d08b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=617d5bf424a71e33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python Sr Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
+          <t>RAG, Copilot, S3, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900a9829c2794aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=b6eaa505c1c3eb5b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Machine Learning (ML) Engineer (AI Insurtech)</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EvolutionIQ</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Keras, BigQuery, Kubernetes, Terraform, BigQuery, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cd074e0f4d340f</t>
+          <t>https://www.indeed.com/viewjob?jk=cc3d33cc6012689e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning (ML) Engineer (AI Insurtech)</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EvolutionIQ</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Keras, BigQuery, Kubernetes, Terraform, BigQuery, Python</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1e470bd9e179e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=add3932f4bb218a9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer- AI Agent</t>
+          <t>Senior Software Engineer – Microservices / MBFF Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shanghai Xiaoxi</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LangChain, Gemini, Prompt Engineering, FastAPI, Kubernetes, CI/CD, NoSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, Cassandra, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bdc304307c73e2</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f4607632479b92</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Practitioner- PRN</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rogers Behavioral Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oconomowoc, WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, FastAPI, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cff99a9854d3ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=253aacc6c05dac30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, User Signal &amp; Ads</t>
+          <t>AI Solution Architect I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kafka, Hadoop, Python, SQL, R, Optimization</t>
+          <t>RAG, Gemini, BigQuery, Dataflow, Kubernetes, CI/CD, BigQuery, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b8ec5f6ed88064c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff985dc809dc176a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Solution Architect II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>REGARD</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, FastAPI, Kubernetes, PySpark, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Gemini, BigQuery, Dataflow, Kubernetes, CI/CD, BigQuery, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8e6412b9b83a76</t>
+          <t>https://www.indeed.com/viewjob?jk=fc112316f08775b4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>REGARD</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Aguadilla, PR, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, FastAPI, Kubernetes, PySpark, PostgreSQL, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, Copilot, TensorFlow, PyTorch, Keras, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb3bea9b095d4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d17df0c1f35a31f2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FULLTHROTTLE</t>
+          <t>OneDigital</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Prompt Engineering, S3, Docker, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Pinecone, Cortex, AKS, CI/CD, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe703dc5462eb40</t>
+          <t>https://www.indeed.com/viewjob?jk=e26052677f506521</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Platform Engineer - Palantir</t>
+          <t>Application Software Engineer, Inference</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Snowflake, Databricks, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9947f29081d0c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=83239a9186090634</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Platform Engineer - Palantir</t>
+          <t>Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Snowflake, Databricks, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, S3, EC2, FastAPI, Docker, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74450422ec001fb7</t>
+          <t>https://www.indeed.com/viewjob?jk=5132b8b5cc64166e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Junior Software QA Engineer</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Telit Wireless Solutions</t>
+          <t>Greenberg Traurig</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Optimization</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, Docker, Kubernetes, Python, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b91213d94efecee</t>
+          <t>https://www.indeed.com/viewjob?jk=8373dc21d10b0d41</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full-Stack Developer – Websites (On Call - Remote)</t>
+          <t>Full-Stack &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>ss8 networks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca49d6a6128d3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=3321c1a088afffc3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Part-time Data Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TNTP</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, NoSQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, XGBoost, CI/CD, Git, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bbf73d5f0d07a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=734bcdd46d224514</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Software Engineer, CRD- New Graduate</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, Git, Snowflake, Kafka, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16d6e07a42496a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3715d19461c0fd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer - Intern - Payments &amp; Wallets</t>
+          <t>Senior Azure Databricks</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,42 +1336,952 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55baa703a2556a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b5b671f2708a31</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>C++ Build and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>Horizon Surgical Systems</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e282700c314ce1b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr Applied Data Scientist - Item Recommendations (applied ML, PyTorch, ML Ops)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1dd6c177e59f46eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>Dallas, TX, US USA</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, Azure ML, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dc046366f632349</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sunnyvale, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c35c983412bb089a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11595b29d0d330c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, PyTorch, Docker, CI/CD, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76d8ab70c151b6ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI Ops Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34d73dafb5674d56</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe03160d5b7f3be3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5465e30e679085e</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>IT Business Applications Analyst II- Hybrid in Fort Myers</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Millennium Physician Group</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Fort Myers, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, Cortex, TensorFlow, PyTorch, Athena, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9524f64bb52fd8ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Engineer III</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, S3, EC2, Kubernetes, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b8f796616ce0e7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Software Development Engineering</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Analog Devices</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, Git, NoSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6458546bef06f3fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Platform Engineer - Palantir</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Acrisure LLC</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Snowflake, Databricks, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bab28965baa78b67</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Shopify Architect</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>S3, Docker, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecfc2fbc843f882c</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Scientist - Energy</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>The Woodlands, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d4d41b0c98de8e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Gen AI Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Paramount Global US Inc</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Avenel, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>10</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e2449a5591f29a5</t>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc30ad9f5cb9493c</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Finance Systems Engineer: Oracle Fusion</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>San Francisco Bay Area, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Data Lake, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90fa6ace46fe2c1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Algorithm engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>KLA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb595f48f4b8fb47</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Java Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>CI/CD, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6edc564c27e6d4e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Python Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Qualis Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LangChain, FastAPI, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be9cb88339f28965</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Engineering Enablement</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MeridianLink</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97b65dbcc323a52b</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Full stack Developer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Limestone Digital</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe40a4087c307a65</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>React Native Developer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Limestone Digital</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c54b92cae6ea4d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Azure Data Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05e67569691d81ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AI Research Scientist PhD (Intern) - United States</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, Docker, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcfe7332a3c8e328</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01fbdd31b9fd056b</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Alchemy Software Solutions</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66475b87d67e3c88</t>
         </is>
       </c>
     </row>
